--- a/SCMH.xlsx
+++ b/SCMH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cliff\Documents\PROJECTS\2026-05 SCMH PCR Selector App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47730817-AB0E-4082-ABBD-BCC09508B571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9734A347-1AB6-4F76-9EBC-3467EB5FA21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="table_long" sheetId="3" r:id="rId1"/>
@@ -22,15 +22,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>Number of Measurements Taken</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>SCMH 3.75 Statistical Product Acceptance Table of 909% Confidence Limits on the Cpk</t>
-  </si>
-  <si>
-    <t>90% Probability that True Cpk Equals or Exceeds:</t>
   </si>
   <si>
     <t>ssize</t>
@@ -40,6 +34,9 @@
   </si>
   <si>
     <t>req_calc_pointest</t>
+  </si>
+  <si>
+    <t>Sample Size</t>
   </si>
 </sst>
 </file>
@@ -170,6 +167,74 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3313599" cy="254557"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D36AC0E1-559E-4BDB-B2A4-8B2F66099371}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="198120"/>
+          <a:ext cx="3313599" cy="254557"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200"/>
+            <a:t>90% Probability that True Cpk Equals or Exceeds:</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -436,13 +501,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>3</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
@@ -2875,828 +2940,827 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A2:L23"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="12" width="12.6640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="6" t="s">
+    <row r="2" spans="1:12" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="6"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+    </row>
+    <row r="3" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="I3" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="J3" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="K3" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="L3" s="3">
         <v>2</v>
-      </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1.3</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1.4</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="H2" s="3">
-        <v>1.6</v>
-      </c>
-      <c r="I2" s="3">
-        <v>1.7</v>
-      </c>
-      <c r="J2" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="K2" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="L2" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>250</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.07</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.17</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.28</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1.42</v>
-      </c>
-      <c r="F3" s="4">
-        <v>1.49</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1.6</v>
-      </c>
-      <c r="H3" s="4">
-        <v>1.7</v>
-      </c>
-      <c r="I3" s="4">
-        <v>1.81</v>
-      </c>
-      <c r="J3" s="4">
-        <v>1.91</v>
-      </c>
-      <c r="K3" s="4">
-        <v>2.02</v>
-      </c>
-      <c r="L3" s="4">
-        <v>2.13</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="B4" s="4">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="C4" s="4">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="D4" s="4">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="E4" s="4">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="F4" s="4">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G4" s="4">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H4" s="4">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I4" s="4">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="J4" s="4">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="K4" s="4">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="L4" s="4">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="B5" s="4">
-        <v>1.0900000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="C5" s="4">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="D5" s="4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="E5" s="4">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="F5" s="4">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="G5" s="4">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H5" s="4">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="I5" s="4">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="J5" s="4">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="K5" s="4">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="L5" s="4">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="B6" s="4">
-        <v>1.1000000000000001</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="C6" s="4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="D6" s="4">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="E6" s="4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="F6" s="4">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G6" s="4">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H6" s="4">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="I6" s="4">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="J6" s="4">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="K6" s="4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="L6" s="4">
-        <v>2.1800000000000002</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="B7" s="4">
-        <v>1.1100000000000001</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C7" s="4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="D7" s="4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="E7" s="4">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="F7" s="4">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="G7" s="4">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H7" s="4">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="I7" s="4">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="J7" s="4">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="K7" s="4">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="L7" s="4">
-        <v>2.21</v>
+        <v>2.1800000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B8" s="4">
-        <v>1.1200000000000001</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="C8" s="4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="D8" s="4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="E8" s="4">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="F8" s="4">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G8" s="4">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H8" s="4">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="I8" s="4">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J8" s="4">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="K8" s="4">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="L8" s="4">
-        <v>2.2200000000000002</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B9" s="4">
-        <v>1.1299999999999999</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="C9" s="4">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="D9" s="4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="E9" s="4">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="F9" s="4">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G9" s="4">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H9" s="4">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="I9" s="4">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="J9" s="4">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="K9" s="4">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="L9" s="4">
-        <v>2.2400000000000002</v>
+        <v>2.2200000000000002</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B10" s="4">
-        <v>1.1399999999999999</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C10" s="4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="D10" s="4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="E10" s="4">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="F10" s="4">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G10" s="4">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="H10" s="4">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="I10" s="4">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="J10" s="4">
-        <v>2.0299999999999998</v>
+        <v>2.02</v>
       </c>
       <c r="K10" s="4">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="L10" s="4">
-        <v>2.2599999999999998</v>
+        <v>2.2400000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B11" s="4">
-        <v>1.1499999999999999</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="C11" s="4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="D11" s="4">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="E11" s="4">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="F11" s="4">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G11" s="4">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H11" s="4">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="I11" s="4">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="J11" s="4">
-        <v>2.06</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="K11" s="4">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="L11" s="4">
-        <v>2.2799999999999998</v>
+        <v>2.2599999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B12" s="4">
-        <v>1.17</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="C12" s="4">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="D12" s="4">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="E12" s="4">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="F12" s="4">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="G12" s="4">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="H12" s="4">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="I12" s="4">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="J12" s="4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="K12" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.17</v>
       </c>
       <c r="L12" s="4">
-        <v>2.31</v>
+        <v>2.2799999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B13" s="4">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="C13" s="4">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="D13" s="4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="E13" s="4">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="F13" s="4">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G13" s="4">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H13" s="4">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="I13" s="4">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="J13" s="4">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="K13" s="4">
-        <v>2.21</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="L13" s="4">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B14" s="4">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="C14" s="4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="D14" s="4">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="E14" s="4">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="F14" s="4">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G14" s="4">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H14" s="4">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="I14" s="4">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="J14" s="4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="K14" s="4">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="L14" s="4">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B15" s="4">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="C15" s="4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="D15" s="4">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="E15" s="4">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="F15" s="4">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="G15" s="4">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H15" s="4">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="I15" s="4">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="K15" s="4">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="L15" s="4">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B16" s="4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="C16" s="4">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="D16" s="4">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="E16" s="4">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="F16" s="4">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G16" s="4">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="H16" s="4">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="I16" s="4">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J16" s="4">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="K16" s="4">
-        <v>2.2799999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="L16" s="4">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B17" s="4">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="C17" s="4">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="D17" s="4">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="E17" s="4">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="F17" s="4">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="G17" s="4">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H17" s="4">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="I17" s="4">
-        <v>2.0699999999999998</v>
+        <v>2.04</v>
       </c>
       <c r="J17" s="4">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="K17" s="4">
-        <v>2.31</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="L17" s="4">
-        <v>2.4300000000000002</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B18" s="4">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="C18" s="4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="D18" s="4">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="E18" s="4">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="F18" s="4">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G18" s="4">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H18" s="4">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="I18" s="4">
-        <v>2.09</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="J18" s="4">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="K18" s="4">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="L18" s="4">
-        <v>2.4500000000000002</v>
+        <v>2.4300000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B19" s="4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="C19" s="4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="D19" s="4">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="E19" s="4">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="F19" s="4">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G19" s="4">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H19" s="4">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="I19" s="4">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="J19" s="4">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="K19" s="4">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="L19" s="4">
-        <v>2.4700000000000002</v>
+        <v>2.4500000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B20" s="4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="C20" s="4">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="D20" s="4">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="E20" s="4">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="F20" s="4">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G20" s="4">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H20" s="4">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="I20" s="4">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="J20" s="4">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="K20" s="4">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="L20" s="4">
-        <v>2.5</v>
+        <v>2.4700000000000002</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B21" s="4">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="C21" s="4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="D21" s="4">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="E21" s="4">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="F21" s="4">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="G21" s="4">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H21" s="4">
-        <v>2.0299999999999998</v>
+        <v>2</v>
       </c>
       <c r="I21" s="4">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="J21" s="4">
-        <v>2.2799999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="K21" s="4">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="L21" s="4">
-        <v>2.5299999999999998</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
+        <v>22</v>
+      </c>
+      <c r="B22" s="4">
+        <v>1.28</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1.53</v>
+      </c>
+      <c r="E22" s="4">
+        <v>1.68</v>
+      </c>
+      <c r="F22" s="4">
+        <v>1.78</v>
+      </c>
+      <c r="G22" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="H22" s="4">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="I22" s="4">
+        <v>2.15</v>
+      </c>
+      <c r="J22" s="4">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="K22" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="L22" s="4">
+        <v>2.5299999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B23" s="4">
         <v>1.3</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C23" s="4">
         <v>1.42</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D23" s="4">
         <v>1.55</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E23" s="4">
         <v>1.71</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F23" s="4">
         <v>1.8</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G23" s="4">
         <v>1.93</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H23" s="4">
         <v>2.06</v>
       </c>
-      <c r="I22" s="4">
+      <c r="I23" s="4">
         <v>2.1800000000000002</v>
       </c>
-      <c r="J22" s="4">
+      <c r="J23" s="4">
         <v>2.31</v>
       </c>
-      <c r="K22" s="4">
+      <c r="K23" s="4">
         <v>2.44</v>
       </c>
-      <c r="L22" s="4">
+      <c r="L23" s="4">
         <v>2.57</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3707,7 +3771,7 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
